--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -1539,6 +1539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1680,6 +1685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1821,6 +1831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1962,6 +1977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2103,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2385,6 +2415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2526,6 +2561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2667,6 +2707,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2808,6 +2853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +2999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3090,6 +3145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4001,6 +4061,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4142,6 +4207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4283,6 +4353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4424,6 +4499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4565,6 +4645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4706,6 +4791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4847,6 +4937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4988,6 +5083,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5129,6 +5229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5270,6 +5375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5411,6 +5521,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5552,6 +5667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6463,6 +6583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6604,6 +6729,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6745,6 +6875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6886,6 +7021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7027,6 +7167,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7168,6 +7313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7309,6 +7459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7450,6 +7605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7591,6 +7751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7873,6 +8043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8014,6 +8189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8925,6 +9105,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9066,6 +9251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9207,6 +9397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9348,6 +9543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9489,6 +9689,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9630,6 +9835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9774,6 +9984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9915,6 +10130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10059,6 +10279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10200,6 +10425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10344,6 +10574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10485,6 +10720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10629,6 +10869,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10770,6 +11015,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10914,6 +11164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11055,6 +11310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11199,6 +11459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11340,6 +11605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11869,6 +12139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12395,6 +12670,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12539,6 +12819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12680,6 +12965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12824,6 +13114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12965,6 +13260,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13109,6 +13409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13250,6 +13555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13394,6 +13704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13535,6 +13850,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13679,6 +13999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13820,6 +14145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13964,6 +14294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14105,6 +14440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14249,6 +14589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14390,6 +14735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14534,6 +14884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14675,6 +15030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14819,6 +15179,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14960,6 +15325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15104,6 +15474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15245,6 +15620,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15389,6 +15769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15528,6 +15913,11 @@
       <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">

--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -1149,11 +1149,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -1171,12 +1166,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1187,11 +1177,6 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1214,22 +1199,22 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1256,17 +1241,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1301,165 +1286,66 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1403,12 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-01</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1534,11 +1420,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1551,22 +1432,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1663,12 +1534,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1680,11 +1551,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1697,22 +1563,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1809,12 +1665,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1826,11 +1682,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1843,22 +1694,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1955,12 +1796,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1972,11 +1813,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1989,22 +1825,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2101,12 +1927,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2118,11 +1944,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1956,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2247,12 +2058,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2264,11 +2075,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2281,22 +2087,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2393,12 +2189,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2410,11 +2206,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2427,22 +2218,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2539,12 +2320,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2556,11 +2337,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2573,22 +2349,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2685,12 +2451,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2702,11 +2468,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2719,22 +2480,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2831,12 +2582,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2848,11 +2599,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2865,22 +2611,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2977,12 +2713,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2994,11 +2730,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3011,22 +2742,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3097,12 +2818,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3123,12 +2844,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3145,73 +2866,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3238,7 +2968,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3283,23 +3013,98 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -3393,17 +3198,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3438,34 +3243,12 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3473,64 +3256,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN19" t="b">
-        <v>1</v>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3538,65 +3263,55 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3343,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3671,87 +3386,63 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -3778,17 +3469,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3809,12 +3500,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3823,165 +3514,66 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R21" t="n">
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN21" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4039,12 +3631,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4056,11 +3648,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4073,22 +3660,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4185,12 +3762,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4202,11 +3779,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4219,22 +3791,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4331,12 +3893,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4348,11 +3910,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4365,22 +3922,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4477,12 +4024,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4494,11 +4041,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4511,22 +4053,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4623,12 +4155,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4640,11 +4172,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4657,22 +4184,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4769,12 +4286,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4786,11 +4303,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4803,22 +4315,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4915,12 +4417,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4932,11 +4434,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4949,22 +4446,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5061,12 +4548,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5078,11 +4565,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5095,22 +4577,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5207,12 +4679,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5224,11 +4696,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5241,22 +4708,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5353,12 +4810,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5370,11 +4827,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5387,22 +4839,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5473,12 +4915,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5499,12 +4941,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5521,73 +4963,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5614,17 +5065,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5645,12 +5096,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5659,81 +5110,165 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5300,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5808,14 +5343,9 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5830,65 +5360,55 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
         <v>1</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5915,17 +5435,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5960,165 +5480,66 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R35" t="n">
+        <v>0</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6150,12 +5571,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6176,12 +5597,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6193,87 +5614,63 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6300,17 +5697,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6331,12 +5728,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6345,165 +5742,66 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R37" t="n">
+        <v>0</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN37" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6561,12 +5859,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6578,11 +5876,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6595,22 +5888,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6707,12 +5990,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6724,11 +6007,6 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6741,22 +6019,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6853,12 +6121,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6870,11 +6138,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6887,22 +6150,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6999,12 +6252,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7016,11 +6269,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7033,22 +6281,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7145,12 +6383,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7162,11 +6400,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7179,22 +6412,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7291,12 +6514,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7308,11 +6531,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7325,22 +6543,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7437,12 +6645,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7454,11 +6662,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7471,22 +6674,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7583,12 +6776,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7600,11 +6793,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7617,22 +6805,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7729,12 +6907,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7746,11 +6924,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7763,22 +6936,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7849,12 +7012,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7875,12 +7038,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7897,73 +7060,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7990,17 +7162,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8021,12 +7193,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8035,81 +7207,165 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN48" t="b">
+        <v>1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8141,12 +7397,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8167,12 +7423,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8184,78 +7440,72 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8287,12 +7537,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8330,87 +7580,63 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8437,17 +7663,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8468,12 +7694,12 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8482,165 +7708,66 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R51" t="n">
+        <v>0</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN51" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8672,12 +7799,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8698,12 +7825,12 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8715,87 +7842,63 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8822,17 +7925,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8853,12 +7956,12 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8867,165 +7970,66 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R53" t="n">
+        <v>0</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN53" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9083,12 +8087,12 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -9100,11 +8104,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9117,22 +8116,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9229,12 +8218,12 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9246,11 +8235,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9263,22 +8247,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9349,12 +8323,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9375,12 +8349,12 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9389,14 +8363,12 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9409,61 +8381,51 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9521,12 +8483,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9538,11 +8500,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9555,22 +8512,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9641,12 +8588,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9667,12 +8614,12 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9681,14 +8628,12 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9701,61 +8646,51 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9813,12 +8748,12 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9830,11 +8765,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9847,22 +8777,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9959,12 +8879,12 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9979,11 +8899,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9996,22 +8911,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10108,12 +9013,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -10125,11 +9030,6 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10142,22 +9042,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10254,12 +9144,12 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10274,11 +9164,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10291,22 +9176,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10403,12 +9278,12 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10420,11 +9295,6 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10437,22 +9307,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10549,12 +9409,12 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10569,11 +9429,6 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10586,22 +9441,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10698,12 +9543,12 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10715,11 +9560,6 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10732,22 +9572,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10844,12 +9674,12 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10864,11 +9694,6 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10881,22 +9706,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10993,12 +9808,12 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -11010,11 +9825,6 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11027,22 +9837,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11113,12 +9913,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -11139,12 +9939,12 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -11153,9 +9953,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11164,73 +9961,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11257,17 +10063,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11288,12 +10094,12 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11302,81 +10108,165 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11434,12 +10324,12 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11454,11 +10344,6 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11471,22 +10356,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11557,12 +10432,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11583,12 +10458,12 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11600,78 +10475,72 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11703,12 +10572,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11746,87 +10615,63 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11853,17 +10698,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11884,12 +10729,12 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11898,165 +10743,69 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN73" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12088,12 +10837,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -12114,12 +10863,12 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -12128,17 +10877,9 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12151,61 +10892,51 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12237,12 +10968,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -12263,12 +10994,12 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -12277,90 +11008,69 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12387,17 +11097,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -12418,12 +11128,12 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12432,165 +11142,66 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R76" t="n">
+        <v>0</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12622,12 +11233,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12648,12 +11259,12 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12662,14 +11273,12 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12682,61 +11291,51 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12768,12 +11367,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12794,12 +11393,12 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12808,17 +11407,9 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12831,61 +11422,51 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12917,12 +11498,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12943,12 +11524,12 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12957,14 +11538,12 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12977,61 +11556,51 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13063,12 +11632,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -13089,12 +11658,12 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -13103,17 +11672,9 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13126,61 +11687,51 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13212,12 +11763,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -13238,12 +11789,12 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -13252,14 +11803,12 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13272,61 +11821,51 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13358,12 +11897,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -13384,12 +11923,12 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13398,17 +11937,9 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13421,61 +11952,51 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13507,12 +12028,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13533,12 +12054,12 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13547,14 +12068,12 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13567,61 +12086,51 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13653,12 +12162,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13679,12 +12188,12 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13693,17 +12202,9 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13716,61 +12217,51 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13802,12 +12293,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13828,12 +12319,12 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13842,14 +12333,12 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13862,61 +12351,51 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13948,12 +12427,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13974,12 +12453,12 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13988,17 +12467,9 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14011,61 +12482,51 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14097,12 +12558,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -14123,12 +12584,12 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -14137,14 +12598,12 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14157,61 +12616,51 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14243,12 +12692,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14269,12 +12718,12 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -14283,17 +12732,9 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14306,61 +12747,51 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14392,12 +12823,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14418,12 +12849,12 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14432,14 +12863,12 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14452,61 +12881,51 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14538,12 +12957,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14564,12 +12983,12 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14578,17 +12997,9 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14601,61 +13012,51 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14687,12 +13088,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14713,12 +13114,12 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14727,14 +13128,12 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14747,61 +13146,51 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14833,12 +13222,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14859,12 +13248,12 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14873,17 +13262,9 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14896,61 +13277,51 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14982,12 +13353,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15008,12 +13379,12 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -15022,14 +13393,12 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15042,61 +13411,51 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
       </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15128,12 +13487,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -15154,12 +13513,12 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -15168,17 +13527,9 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15191,795 +13542,49 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>2009-10-01</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2009-10</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
-      <c r="AT95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV95" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA95" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB95" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC95" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>2009-11-01</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP96" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
-      <c r="AT96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV96" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA96" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB96" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC96" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>2009-11-01</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP97" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
-      <c r="AT97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV97" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA97" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB97" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC97" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP98" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
-      <c r="AT98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV98" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA98" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB98" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC98" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
-      <c r="AT99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV99" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA99" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB99" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -16111,7 +13716,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -16131,7 +13736,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -16141,7 +13746,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -1149,6 +1149,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -1166,7 +1171,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1177,6 +1187,11 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1199,22 +1214,22 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1241,17 +1256,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1286,66 +1301,165 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1517,12 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1534,12 +1648,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1665,12 +1779,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1796,12 +1910,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1927,12 +2041,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2058,12 +2172,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2189,12 +2303,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2320,12 +2434,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2451,12 +2565,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2582,12 +2696,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2713,12 +2827,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2818,12 +2932,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2844,12 +2958,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2861,87 +2975,63 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2968,7 +3058,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3013,98 +3103,23 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -3198,17 +3213,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3243,12 +3258,34 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3256,6 +3293,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3263,55 +3358,65 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3448,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3386,63 +3491,87 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3598,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3500,12 +3629,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3514,66 +3643,165 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3859,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3762,12 +3990,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3893,12 +4121,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4024,12 +4252,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4155,12 +4383,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4286,12 +4514,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4417,12 +4645,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4548,12 +4776,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4679,12 +4907,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4810,12 +5038,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -4915,12 +5143,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4941,12 +5169,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -4958,87 +5186,63 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5065,17 +5269,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5096,12 +5300,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5110,165 +5314,66 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R33" t="n">
+        <v>0</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5405,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5343,9 +5448,14 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5360,55 +5470,65 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
         <v>1</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5435,17 +5555,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5480,66 +5600,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5790,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5597,12 +5816,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5614,63 +5833,87 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5697,17 +5940,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5728,12 +5971,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5742,66 +5985,165 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5859,12 +6201,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -5990,12 +6332,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6121,12 +6463,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6252,12 +6594,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6383,12 +6725,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6514,12 +6856,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6645,12 +6987,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6776,12 +7118,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6907,12 +7249,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7012,12 +7354,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7038,12 +7380,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7055,87 +7397,63 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7162,17 +7480,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7193,12 +7511,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7207,165 +7525,66 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R48" t="n">
+        <v>0</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN48" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7397,12 +7616,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7423,12 +7642,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7440,19 +7659,14 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -7460,52 +7674,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7747,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7580,63 +7790,87 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7663,17 +7897,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7694,12 +7928,12 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -7708,66 +7942,165 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7799,12 +8132,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7825,12 +8158,12 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -7842,63 +8175,87 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7925,17 +8282,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7956,12 +8313,12 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -7970,66 +8327,165 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8543,12 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8218,12 +8674,12 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8323,12 +8779,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8349,21 +8805,18 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
@@ -8390,42 +8843,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8483,12 +8936,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -8588,12 +9041,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8614,21 +9067,18 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
@@ -8655,42 +9105,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8748,12 +9198,12 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -8879,12 +9329,12 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9013,12 +9463,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9144,12 +9594,12 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9278,12 +9728,12 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9409,12 +9859,12 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -9543,12 +9993,12 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -9674,12 +10124,12 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -9808,12 +10258,12 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -9913,12 +10363,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9939,12 +10389,12 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -9953,90 +10403,69 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10063,17 +10492,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10094,12 +10523,12 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10108,165 +10537,66 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R69" t="n">
+        <v>0</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10654,12 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -10432,12 +10762,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10458,12 +10788,12 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -10475,19 +10805,14 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
@@ -10495,52 +10820,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10572,12 +10893,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10615,63 +10936,87 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10698,17 +11043,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10729,12 +11074,12 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -10743,69 +11088,165 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10837,12 +11278,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10863,18 +11304,21 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N74" t="n">
         <v>0</v>
       </c>
       <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
@@ -10901,42 +11345,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10968,12 +11412,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10994,12 +11438,12 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11008,69 +11452,90 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11097,17 +11562,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11128,12 +11593,12 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11142,66 +11607,165 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11233,12 +11797,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11259,21 +11823,18 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N77" t="n">
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
@@ -11300,42 +11861,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11367,12 +11928,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11393,18 +11954,21 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
@@ -11431,42 +11995,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11498,12 +12062,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11524,21 +12088,18 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
@@ -11565,42 +12126,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11632,12 +12193,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11658,18 +12219,21 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N80" t="n">
         <v>0</v>
       </c>
       <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
@@ -11696,42 +12260,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11763,12 +12327,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11789,21 +12353,18 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N81" t="n">
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
@@ -11830,42 +12391,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11897,12 +12458,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -11923,18 +12484,21 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N82" t="n">
         <v>0</v>
       </c>
       <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
@@ -11961,42 +12525,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12028,12 +12592,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12054,21 +12618,18 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
@@ -12095,42 +12656,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12723,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12188,18 +12749,21 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N84" t="n">
         <v>0</v>
       </c>
       <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
@@ -12226,42 +12790,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12293,12 +12857,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12319,21 +12883,18 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N85" t="n">
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
@@ -12360,42 +12921,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12427,12 +12988,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12453,18 +13014,21 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N86" t="n">
         <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
@@ -12491,42 +13055,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12558,12 +13122,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12584,21 +13148,18 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
@@ -12625,42 +13186,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12692,12 +13253,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -12718,18 +13279,21 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
@@ -12756,42 +13320,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12823,12 +13387,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -12849,21 +13413,18 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
@@ -12890,42 +13451,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12957,12 +13518,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12983,18 +13544,21 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
@@ -13021,42 +13585,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13088,12 +13652,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13114,21 +13678,18 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
@@ -13155,42 +13716,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13222,12 +13783,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13248,18 +13809,21 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
@@ -13286,42 +13850,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13353,12 +13917,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13379,21 +13943,18 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
@@ -13420,42 +13981,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13487,12 +14048,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13513,18 +14074,21 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
@@ -13551,40 +14115,701 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW94" t="inlineStr">
+      <c r="AW95" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
+      <c r="AX95" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY94" t="inlineStr">
+      <c r="AY95" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA94" t="inlineStr">
+      <c r="BA95" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB94" t="inlineStr">
+      <c r="BB95" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC94" t="inlineStr">
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -13716,7 +14941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -13736,7 +14961,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -13746,7 +14971,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -1534,6 +1534,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1546,12 +1551,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1665,6 +1680,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1677,12 +1697,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1796,6 +1826,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1808,12 +1843,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1927,6 +1972,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1939,12 +1989,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2058,6 +2118,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2070,12 +2135,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2189,6 +2264,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2201,12 +2281,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2320,6 +2410,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2332,12 +2427,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2451,6 +2556,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2463,12 +2573,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2582,6 +2702,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2594,12 +2719,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2713,6 +2848,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2725,12 +2865,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2844,6 +2994,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2856,12 +3011,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2975,6 +3140,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2987,12 +3157,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3876,6 +4056,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3888,12 +4073,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4007,6 +4202,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4019,12 +4219,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4138,6 +4348,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4150,12 +4365,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4269,6 +4494,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4281,12 +4511,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4400,6 +4640,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4412,12 +4657,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4531,6 +4786,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4543,12 +4803,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4662,6 +4932,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4674,12 +4949,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4793,6 +5078,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4805,12 +5095,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4924,6 +5224,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4936,12 +5241,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5055,6 +5370,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5067,12 +5387,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5186,6 +5516,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5198,12 +5533,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5317,6 +5662,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5329,12 +5679,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6218,6 +6578,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6230,12 +6595,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6349,6 +6724,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6361,12 +6741,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6480,6 +6870,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6492,12 +6887,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6611,6 +7016,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6623,12 +7033,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6742,6 +7162,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6754,12 +7179,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6873,6 +7308,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6885,12 +7325,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7004,6 +7454,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7016,12 +7471,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7135,6 +7600,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7147,12 +7617,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7266,6 +7746,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7278,12 +7763,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7397,6 +7892,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7409,12 +7909,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7528,6 +8038,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7540,12 +8055,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7659,6 +8184,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7671,12 +8201,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8560,6 +9100,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8572,12 +9117,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8691,6 +9246,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8703,12 +9263,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8822,6 +9392,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8834,12 +9409,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8953,6 +9538,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8965,12 +9555,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9084,6 +9684,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9096,12 +9701,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9215,6 +9830,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9227,12 +9847,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9349,6 +9979,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9361,12 +9996,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9480,6 +10125,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9492,12 +10142,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9614,6 +10274,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9626,12 +10291,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9745,6 +10420,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9757,12 +10437,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9879,6 +10569,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9891,12 +10586,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10010,6 +10715,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10022,12 +10732,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10144,6 +10864,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10156,12 +10881,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10275,6 +11010,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10287,12 +11027,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10409,6 +11159,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10421,12 +11176,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10540,6 +11305,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10552,12 +11322,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10674,6 +11454,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10686,12 +11471,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10805,6 +11600,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10817,12 +11617,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11324,6 +12134,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11336,12 +12151,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11840,6 +12665,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11852,12 +12682,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11974,6 +12814,11 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11986,12 +12831,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12105,6 +12960,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12117,12 +12977,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12239,6 +13109,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12251,12 +13126,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12370,6 +13255,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12382,12 +13272,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12504,6 +13404,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12516,12 +13421,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12635,6 +13550,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12647,12 +13567,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12769,6 +13699,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12781,12 +13716,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12900,6 +13845,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12912,12 +13862,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13034,6 +13994,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13046,12 +14011,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13165,6 +14140,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13177,12 +14157,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13299,6 +14289,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13311,12 +14306,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13430,6 +14435,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13442,12 +14452,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13564,6 +14584,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13576,12 +14601,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13695,6 +14730,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13707,12 +14747,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13829,6 +14879,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13841,12 +14896,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13960,6 +15025,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13972,12 +15042,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14094,6 +15174,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14106,12 +15191,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14225,6 +15320,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14237,12 +15337,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14359,6 +15469,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14371,12 +15486,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14490,6 +15615,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14502,12 +15632,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14624,6 +15764,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14636,12 +15781,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14755,6 +15910,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14767,12 +15927,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
